--- a/재고수불부_컬럼정의서.xlsx
+++ b/재고수불부_컬럼정의서.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -113,6 +113,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,6 +493,8 @@
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="62" customWidth="1" min="7" max="7"/>
     <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -533,6 +538,16 @@
           <t>Redash SQL 힌트</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BOM유형</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>BOM전개소요수량</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -575,6 +590,16 @@
           <t>DATE(updated_at AT TIME ZONE 'Asia/Seoul') AS dt</t>
         </is>
       </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>BOM유형</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>BOM전개소요수량</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -617,6 +642,16 @@
           <t>GROUP BY DATE(updated_at AT TIME ZONE 'Asia/Seoul'), sku_id</t>
         </is>
       </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>해당 SKU의 BOM 분류</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>배송완료 건 기준 BOM 전개 소요수량 합계</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -657,6 +692,16 @@
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>LEFT JOIN sku_ro ON sku_ro.id = stock_usage_ro.sku_id</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>SINGLE (BOM 없음) / BOM완제품 (하위 구성요소 있음) / BOM구성요소 (상위 완제품의 부품)</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>경로A: 완제품 배송수량 × BOM단위수량 / 경로B: 구성요소 직접 배송수량</t>
         </is>
       </c>
     </row>
